--- a/warehouseStockspricesfinal.xlsx
+++ b/warehouseStockspricesfinal.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Product_Name</t>
   </si>
@@ -39,6 +39,42 @@
   </si>
   <si>
     <t>2B_URL</t>
+  </si>
+  <si>
+    <t>Apple iPhone 13 (128GB)</t>
+  </si>
+  <si>
+    <t>https://dubaiphone.net/en/product/apple-iphone-13-128gb-midnight</t>
+  </si>
+  <si>
+    <t>https://dream2000.com/apple-iphone-13-128gb-ram-4gb-midnight.html</t>
+  </si>
+  <si>
+    <t>https://2b.com.eg/en/apple-iphone-13-128gb-midnight.html</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy A17</t>
+  </si>
+  <si>
+    <t>https://dubaiphone.net/ar/samsung-galaxy-a17</t>
+  </si>
+  <si>
+    <t>https://dream2000.com/mobiles/samsung-galaxy-a17.html</t>
+  </si>
+  <si>
+    <t>https://2b.com.eg/en/samsung-galaxy-a17-4g-6gb-ram-128gb-gray.html</t>
+  </si>
+  <si>
+    <t>Xiaomi Redmi Note 13</t>
+  </si>
+  <si>
+    <t>https://dubaiphone.net/ar/product/xiaomi-redmi-note-13-8gb-ram-128gb-rom-midnight-black</t>
+  </si>
+  <si>
+    <t>https://dream2000.com/mobile-xiaomi-redmi-note-13-8gb-ram-128gb-midnight-black.html</t>
+  </si>
+  <si>
+    <t>https://2b.com.eg/ar/xiaomi-redmi-note-13-6gb-ram-128gb-black.html</t>
   </si>
 </sst>
 </file>
@@ -51,9 +87,16 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
+  <fonts count="24">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -70,6 +113,22 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -538,145 +597,163 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1211,30 +1288,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="39.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="25.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="25.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="20.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="39.5555555555556" style="2" customWidth="1"/>
+    <col min="2" max="2" width="89.2222222222222" style="3" customWidth="1"/>
+    <col min="3" max="3" width="88.2222222222222" style="3" customWidth="1"/>
+    <col min="4" max="4" width="70.7777777777778" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:4">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:4">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B4" r:id="rId1" display="https://dubaiphone.net/ar/product/xiaomi-redmi-note-13-8gb-ram-128gb-rom-midnight-black"/>
+    <hyperlink ref="C4" r:id="rId2" display="https://dream2000.com/mobile-xiaomi-redmi-note-13-8gb-ram-128gb-midnight-black.html"/>
+    <hyperlink ref="D4" r:id="rId3" display="https://2b.com.eg/ar/xiaomi-redmi-note-13-6gb-ram-128gb-black.html"/>
+    <hyperlink ref="B3" r:id="rId4" display="https://dubaiphone.net/ar/samsung-galaxy-a17" tooltip="https://dubaiphone.net/ar/samsung-galaxy-a17"/>
+    <hyperlink ref="C3" r:id="rId5" display="https://dream2000.com/mobiles/samsung-galaxy-a17.html" tooltip="https://dream2000.com/mobiles/samsung-galaxy-a17.html"/>
+    <hyperlink ref="D3" r:id="rId6" display="https://2b.com.eg/en/samsung-galaxy-a17-4g-6gb-ram-128gb-gray.html" tooltip="https://2b.com.eg/en/samsung-galaxy-a17-4g-6gb-ram-128gb-gray.html"/>
+    <hyperlink ref="B2" r:id="rId7" display="https://dubaiphone.net/en/product/apple-iphone-13-128gb-midnight"/>
+    <hyperlink ref="C2" r:id="rId8" display="https://dream2000.com/apple-iphone-13-128gb-ram-4gb-midnight.html"/>
+    <hyperlink ref="D2" r:id="rId9" display="https://2b.com.eg/en/apple-iphone-13-128gb-midnight.html"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
